--- a/output/isabel-cohorts/김건희반_시험수준별_성적.xlsx
+++ b/output/isabel-cohorts/김건희반_시험수준별_성적.xlsx
@@ -4059,11 +4059,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="26484043"/>
-        <c:axId val="91941593"/>
+        <c:axId val="16120816"/>
+        <c:axId val="4384924"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="26484043"/>
+        <c:axId val="16120816"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4095,7 +4095,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="91941593"/>
+        <c:crossAx val="4384924"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4103,7 +4103,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="91941593"/>
+        <c:axId val="4384924"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -4181,7 +4181,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="26484043"/>
+        <c:crossAx val="16120816"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="10"/>
@@ -4782,11 +4782,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="44054814"/>
-        <c:axId val="41613399"/>
+        <c:axId val="33706912"/>
+        <c:axId val="67707653"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="44054814"/>
+        <c:axId val="33706912"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4818,7 +4818,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="41613399"/>
+        <c:crossAx val="67707653"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4826,7 +4826,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="41613399"/>
+        <c:axId val="67707653"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="17"/>
@@ -4904,7 +4904,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="44054814"/>
+        <c:crossAx val="33706912"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -5505,11 +5505,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="57706176"/>
-        <c:axId val="67529369"/>
+        <c:axId val="7228946"/>
+        <c:axId val="33739506"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="57706176"/>
+        <c:axId val="7228946"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5541,7 +5541,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="67529369"/>
+        <c:crossAx val="33739506"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5549,7 +5549,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="67529369"/>
+        <c:axId val="33739506"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="28"/>
@@ -5627,7 +5627,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="57706176"/>
+        <c:crossAx val="7228946"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="2"/>
@@ -6156,11 +6156,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="97409257"/>
-        <c:axId val="87612243"/>
+        <c:axId val="38131127"/>
+        <c:axId val="71045527"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="97409257"/>
+        <c:axId val="38131127"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6192,7 +6192,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="87612243"/>
+        <c:crossAx val="71045527"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6200,7 +6200,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="87612243"/>
+        <c:axId val="71045527"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -6278,7 +6278,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="97409257"/>
+        <c:crossAx val="38131127"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="10"/>
@@ -6807,11 +6807,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="85980693"/>
-        <c:axId val="34077085"/>
+        <c:axId val="61062157"/>
+        <c:axId val="63882275"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="85980693"/>
+        <c:axId val="61062157"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6843,7 +6843,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="34077085"/>
+        <c:crossAx val="63882275"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6851,7 +6851,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="34077085"/>
+        <c:axId val="63882275"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="17"/>
@@ -6929,7 +6929,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="85980693"/>
+        <c:crossAx val="61062157"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -7458,11 +7458,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="10724691"/>
-        <c:axId val="55403330"/>
+        <c:axId val="74304810"/>
+        <c:axId val="59914746"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="10724691"/>
+        <c:axId val="74304810"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7494,7 +7494,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="55403330"/>
+        <c:crossAx val="59914746"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7502,7 +7502,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="55403330"/>
+        <c:axId val="59914746"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="28"/>
@@ -7580,7 +7580,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="10724691"/>
+        <c:crossAx val="74304810"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="2"/>
@@ -8050,11 +8050,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="85540189"/>
-        <c:axId val="87291552"/>
+        <c:axId val="11124446"/>
+        <c:axId val="35582179"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="85540189"/>
+        <c:axId val="11124446"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8086,7 +8086,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="87291552"/>
+        <c:crossAx val="35582179"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8094,7 +8094,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="87291552"/>
+        <c:axId val="35582179"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -8172,7 +8172,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="85540189"/>
+        <c:crossAx val="11124446"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="10"/>
@@ -8642,11 +8642,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="2736017"/>
-        <c:axId val="4570699"/>
+        <c:axId val="13059420"/>
+        <c:axId val="8362025"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="2736017"/>
+        <c:axId val="13059420"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8678,7 +8678,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="4570699"/>
+        <c:crossAx val="8362025"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8686,7 +8686,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="4570699"/>
+        <c:axId val="8362025"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="17"/>
@@ -8764,7 +8764,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2736017"/>
+        <c:crossAx val="13059420"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -9234,11 +9234,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="56821201"/>
-        <c:axId val="83277225"/>
+        <c:axId val="19199007"/>
+        <c:axId val="4904857"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="56821201"/>
+        <c:axId val="19199007"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9270,7 +9270,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="83277225"/>
+        <c:crossAx val="4904857"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -9278,7 +9278,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="83277225"/>
+        <c:axId val="4904857"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="28"/>
@@ -9356,7 +9356,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="56821201"/>
+        <c:crossAx val="19199007"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="2"/>

--- a/output/isabel-cohorts/김건희반_시험수준별_성적.xlsx
+++ b/output/isabel-cohorts/김건희반_시험수준별_성적.xlsx
@@ -4059,11 +4059,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="16120816"/>
-        <c:axId val="4384924"/>
+        <c:axId val="53266507"/>
+        <c:axId val="63816366"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="16120816"/>
+        <c:axId val="53266507"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4095,7 +4095,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="4384924"/>
+        <c:crossAx val="63816366"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4103,7 +4103,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="4384924"/>
+        <c:axId val="63816366"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -4181,7 +4181,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="16120816"/>
+        <c:crossAx val="53266507"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="10"/>
@@ -4782,11 +4782,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="33706912"/>
-        <c:axId val="67707653"/>
+        <c:axId val="8941886"/>
+        <c:axId val="13232281"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="33706912"/>
+        <c:axId val="8941886"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4818,7 +4818,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="67707653"/>
+        <c:crossAx val="13232281"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4826,7 +4826,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="67707653"/>
+        <c:axId val="13232281"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="17"/>
@@ -4904,7 +4904,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="33706912"/>
+        <c:crossAx val="8941886"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -5505,11 +5505,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="7228946"/>
-        <c:axId val="33739506"/>
+        <c:axId val="91153194"/>
+        <c:axId val="87260075"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="7228946"/>
+        <c:axId val="91153194"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5541,7 +5541,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="33739506"/>
+        <c:crossAx val="87260075"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5549,7 +5549,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="33739506"/>
+        <c:axId val="87260075"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="28"/>
@@ -5627,7 +5627,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="7228946"/>
+        <c:crossAx val="91153194"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="2"/>
@@ -6156,11 +6156,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="38131127"/>
-        <c:axId val="71045527"/>
+        <c:axId val="97926984"/>
+        <c:axId val="27158910"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="38131127"/>
+        <c:axId val="97926984"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6192,7 +6192,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="71045527"/>
+        <c:crossAx val="27158910"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6200,7 +6200,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="71045527"/>
+        <c:axId val="27158910"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -6278,7 +6278,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="38131127"/>
+        <c:crossAx val="97926984"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="10"/>
@@ -6807,11 +6807,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="61062157"/>
-        <c:axId val="63882275"/>
+        <c:axId val="76524398"/>
+        <c:axId val="56673355"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="61062157"/>
+        <c:axId val="76524398"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6843,7 +6843,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="63882275"/>
+        <c:crossAx val="56673355"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6851,7 +6851,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="63882275"/>
+        <c:axId val="56673355"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="17"/>
@@ -6929,7 +6929,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="61062157"/>
+        <c:crossAx val="76524398"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -7458,11 +7458,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="74304810"/>
-        <c:axId val="59914746"/>
+        <c:axId val="30067446"/>
+        <c:axId val="7057206"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="74304810"/>
+        <c:axId val="30067446"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7494,7 +7494,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="59914746"/>
+        <c:crossAx val="7057206"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7502,7 +7502,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="59914746"/>
+        <c:axId val="7057206"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="28"/>
@@ -7580,7 +7580,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="74304810"/>
+        <c:crossAx val="30067446"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="2"/>
@@ -8050,11 +8050,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="11124446"/>
-        <c:axId val="35582179"/>
+        <c:axId val="53542463"/>
+        <c:axId val="58294280"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="11124446"/>
+        <c:axId val="53542463"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8086,7 +8086,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="35582179"/>
+        <c:crossAx val="58294280"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8094,7 +8094,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="35582179"/>
+        <c:axId val="58294280"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -8172,7 +8172,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="11124446"/>
+        <c:crossAx val="53542463"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="10"/>
@@ -8642,11 +8642,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="13059420"/>
-        <c:axId val="8362025"/>
+        <c:axId val="22830186"/>
+        <c:axId val="29459036"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="13059420"/>
+        <c:axId val="22830186"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8678,7 +8678,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="8362025"/>
+        <c:crossAx val="29459036"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8686,7 +8686,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="8362025"/>
+        <c:axId val="29459036"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="17"/>
@@ -8764,7 +8764,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="13059420"/>
+        <c:crossAx val="22830186"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -9234,11 +9234,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="19199007"/>
-        <c:axId val="4904857"/>
+        <c:axId val="35256975"/>
+        <c:axId val="7243007"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="19199007"/>
+        <c:axId val="35256975"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9270,7 +9270,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="4904857"/>
+        <c:crossAx val="7243007"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -9278,7 +9278,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="4904857"/>
+        <c:axId val="7243007"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="28"/>
@@ -9356,7 +9356,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="19199007"/>
+        <c:crossAx val="35256975"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="2"/>

--- a/output/isabel-cohorts/김건희반_시험수준별_성적.xlsx
+++ b/output/isabel-cohorts/김건희반_시험수준별_성적.xlsx
@@ -4059,11 +4059,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="53266507"/>
-        <c:axId val="63816366"/>
+        <c:axId val="11098277"/>
+        <c:axId val="67818229"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="53266507"/>
+        <c:axId val="11098277"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4095,7 +4095,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="63816366"/>
+        <c:crossAx val="67818229"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4103,7 +4103,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="63816366"/>
+        <c:axId val="67818229"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -4181,7 +4181,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="53266507"/>
+        <c:crossAx val="11098277"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="10"/>
@@ -4782,11 +4782,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="8941886"/>
-        <c:axId val="13232281"/>
+        <c:axId val="35948983"/>
+        <c:axId val="38237594"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="8941886"/>
+        <c:axId val="35948983"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4818,7 +4818,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="13232281"/>
+        <c:crossAx val="38237594"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4826,7 +4826,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="13232281"/>
+        <c:axId val="38237594"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="17"/>
@@ -4904,7 +4904,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="8941886"/>
+        <c:crossAx val="35948983"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -5505,11 +5505,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="91153194"/>
-        <c:axId val="87260075"/>
+        <c:axId val="26384484"/>
+        <c:axId val="2055344"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="91153194"/>
+        <c:axId val="26384484"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5541,7 +5541,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="87260075"/>
+        <c:crossAx val="2055344"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5549,7 +5549,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="87260075"/>
+        <c:axId val="2055344"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="28"/>
@@ -5627,7 +5627,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="91153194"/>
+        <c:crossAx val="26384484"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="2"/>
@@ -6156,11 +6156,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="97926984"/>
-        <c:axId val="27158910"/>
+        <c:axId val="31857547"/>
+        <c:axId val="31658471"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="97926984"/>
+        <c:axId val="31857547"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6192,7 +6192,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="27158910"/>
+        <c:crossAx val="31658471"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6200,7 +6200,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="27158910"/>
+        <c:axId val="31658471"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -6278,7 +6278,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="97926984"/>
+        <c:crossAx val="31857547"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="10"/>
@@ -6807,11 +6807,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="76524398"/>
-        <c:axId val="56673355"/>
+        <c:axId val="61257405"/>
+        <c:axId val="2740124"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="76524398"/>
+        <c:axId val="61257405"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6843,7 +6843,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="56673355"/>
+        <c:crossAx val="2740124"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6851,7 +6851,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="56673355"/>
+        <c:axId val="2740124"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="17"/>
@@ -6929,7 +6929,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="76524398"/>
+        <c:crossAx val="61257405"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -7458,11 +7458,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="30067446"/>
-        <c:axId val="7057206"/>
+        <c:axId val="84694380"/>
+        <c:axId val="39120460"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="30067446"/>
+        <c:axId val="84694380"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7494,7 +7494,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="7057206"/>
+        <c:crossAx val="39120460"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7502,7 +7502,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="7057206"/>
+        <c:axId val="39120460"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="28"/>
@@ -7580,7 +7580,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="30067446"/>
+        <c:crossAx val="84694380"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="2"/>
@@ -8050,11 +8050,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="53542463"/>
-        <c:axId val="58294280"/>
+        <c:axId val="82099301"/>
+        <c:axId val="83627557"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="53542463"/>
+        <c:axId val="82099301"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8086,7 +8086,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="58294280"/>
+        <c:crossAx val="83627557"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8094,7 +8094,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="58294280"/>
+        <c:axId val="83627557"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -8172,7 +8172,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="53542463"/>
+        <c:crossAx val="82099301"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="10"/>
@@ -8642,11 +8642,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="22830186"/>
-        <c:axId val="29459036"/>
+        <c:axId val="9014281"/>
+        <c:axId val="2359840"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="22830186"/>
+        <c:axId val="9014281"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8678,7 +8678,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="29459036"/>
+        <c:crossAx val="2359840"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8686,7 +8686,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="29459036"/>
+        <c:axId val="2359840"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="17"/>
@@ -8764,7 +8764,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="22830186"/>
+        <c:crossAx val="9014281"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -9234,11 +9234,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="35256975"/>
-        <c:axId val="7243007"/>
+        <c:axId val="61288399"/>
+        <c:axId val="41262764"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="35256975"/>
+        <c:axId val="61288399"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9270,7 +9270,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="7243007"/>
+        <c:crossAx val="41262764"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -9278,7 +9278,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="7243007"/>
+        <c:axId val="41262764"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="28"/>
@@ -9356,7 +9356,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="35256975"/>
+        <c:crossAx val="61288399"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="2"/>
